--- a/output/means.xlsx
+++ b/output/means.xlsx
@@ -303,16 +303,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>44.6242603550296</v>
+        <v>44.4430769230769</v>
       </c>
       <c r="C2" s="4">
-        <v>28.4071051771253</v>
+        <v>28.384267179467</v>
       </c>
       <c r="D2" s="4">
-        <v>203.80118694362</v>
+        <v>202.953703703704</v>
       </c>
       <c r="E2" s="4">
-        <v>174.961538461538</v>
+        <v>174.566153846154</v>
       </c>
       <c r="F2" s="4">
         <v>4.73040000181908</v>

--- a/output/means.xlsx
+++ b/output/means.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="###0.000"/>
+    <numFmt numFmtId="164" formatCode="#####0.0"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -271,10 +271,10 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="11" customHeight="1" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="9.71" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.71" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.71" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.71" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.71" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.71" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.71" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.71" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.71" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
